--- a/template_absen.xlsx
+++ b/template_absen.xlsx
@@ -251,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -356,6 +356,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -785,13 +788,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:F18"/>
+  <dimension ref="B3:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.77734375" customWidth="1" style="33" min="2" max="2"/>
-    <col width="11" customWidth="1" style="33" min="3" max="4"/>
-    <col width="11.88671875" customWidth="1" style="33" min="5" max="5"/>
-    <col width="14.6640625" customWidth="1" style="33" min="6" max="6"/>
+    <col width="20.78" customWidth="1" style="33" min="2" max="2"/>
+    <col width="11" customWidth="1" style="33" min="3" max="3"/>
+    <col width="11" customWidth="1" style="33" min="4" max="4"/>
+    <col width="11.89" customWidth="1" style="33" min="5" max="5"/>
+    <col width="30" customWidth="1" style="33" min="6" max="6"/>
+    <col width="14.66" customWidth="1" style="33" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="3" ht="15.75" customHeight="1" s="33">
@@ -805,7 +810,7 @@
           <t>: {nama}</t>
         </is>
       </c>
-      <c r="F3" s="37" t="n"/>
+      <c r="G3" s="37" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" s="33">
       <c r="B4" t="inlineStr">
@@ -818,7 +823,7 @@
           <t>: {unit_kerja}</t>
         </is>
       </c>
-      <c r="F4" s="37" t="n"/>
+      <c r="G4" s="37" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="33">
       <c r="B5" t="inlineStr">
@@ -831,10 +836,10 @@
           <t>: {no_rek}</t>
         </is>
       </c>
-      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="37" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="33">
-      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="33">
       <c r="B7" s="34" t="inlineStr">
@@ -857,7 +862,12 @@
           <t>Keterangan</t>
         </is>
       </c>
-      <c r="F7" s="38" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>Izin</t>
+        </is>
+      </c>
+      <c r="G7" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Biaya Makan </t>
         </is>
@@ -878,33 +888,40 @@
           <t>Hadir</t>
         </is>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="33">
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="42" t="n">
         <v>46284</v>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Libur </t>
         </is>
       </c>
-      <c r="D9" s="43" t="n"/>
-      <c r="E9" s="43" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
       <c r="F9" s="44" t="n"/>
+      <c r="G9" s="45" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="33">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>JUMLAH</t>
         </is>
       </c>
-      <c r="C10" s="43" t="n"/>
-      <c r="D10" s="43" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
       <c r="E10" s="44" t="n"/>
-      <c r="F10" s="46" t="n"/>
+      <c r="F10" s="45" t="n"/>
+      <c r="G10" s="47" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
@@ -912,36 +929,36 @@
           <t xml:space="preserve">yang bersangkutan, </t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Makassar, {tanggal_ttd}</t>
         </is>
       </c>
-      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="22" t="n"/>
       <c r="C13" s="22" t="n"/>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">PT. Bank Sulselbar </t>
         </is>
       </c>
-      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
     </row>
     <row r="14">
-      <c r="E14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>{divisi}</t>
         </is>
       </c>
-      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="37" t="n"/>
     </row>
     <row r="16">
-      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="37" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="33">
       <c r="B17" s="21" t="inlineStr">
@@ -949,12 +966,12 @@
           <t>{nama}</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Faisal Hafiz </t>
         </is>
       </c>
-      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="37" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1" s="33">
       <c r="B18" s="23" t="inlineStr">
@@ -962,19 +979,19 @@
           <t xml:space="preserve">Magang </t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Pimdept. Risiko Operasional, TI &amp; Lainnya</t>
         </is>
       </c>
-      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="C9:G9"/>
     <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
